--- a/api/templates/genexpert_issues/es.xlsx
+++ b/api/templates/genexpert_issues/es.xlsx
@@ -1,175 +1,161 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet sheetId="1" name="Results" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
-    <t xml:space="preserve">Problemas de GeneXpert</t>
+    <t>Problemas de GeneXpert</t>
   </si>
   <si>
-    <t xml:space="preserve">Entre fechas: &lt;Dates&gt;</t>
+    <t>Entre fechas: &lt;Dates&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Estados: &lt;States&gt;</t>
+    <t>Estados: &lt;States&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Ciudad: &lt;Lgas&gt;</t>
+    <t>Ciudad: &lt;Lgas&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Sitios: &lt;Sites&gt;</t>
+    <t>Sitios: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;Table&gt;</t>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Disparado en</t>
+    <t>&lt;Table&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Sitio</t>
+    <t>Disparado en</t>
   </si>
   <si>
-    <t xml:space="preserve">Nro. Serie instrumento</t>
+    <t>Sitio</t>
   </si>
   <si>
-    <t xml:space="preserve">Error</t>
+    <t>Nro. Serie instrumento</t>
   </si>
   <si>
-    <t xml:space="preserve">Código de Error</t>
+    <t>Error</t>
   </si>
   <si>
-    <t xml:space="preserve">Total Resultados</t>
+    <t>Código de Error</t>
   </si>
   <si>
-    <t xml:space="preserve">Errores</t>
+    <t>Total Resultados</t>
   </si>
   <si>
-    <t xml:space="preserve">Porcentaje de Error</t>
+    <t>Errores</t>
   </si>
   <si>
-    <t xml:space="preserve">Módulo</t>
+    <t>Porcentaje de Error</t>
   </si>
   <si>
-    <t xml:space="preserve">Lote</t>
+    <t>Módulo</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;triggeredOn&gt;</t>
+    <t>Lote</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;siteName&gt;</t>
+    <t>&lt;triggeredOn&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;instrumentSerial&gt;</t>
+    <t>&lt;siteName&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;error&gt;</t>
+    <t>&lt;instrumentSerial&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;errorCodes&gt;</t>
+    <t>&lt;error&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;totalResults&gt;</t>
+    <t>&lt;errorCodes&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;resultsWithErrors&gt;</t>
+    <t>&lt;totalResults&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;errorPercentage&gt;</t>
+    <t>&lt;resultsWithErrors&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;moduleSerial&gt;</t>
+    <t>&lt;errorPercentage&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;consumableLot&gt;</t>
+    <t>&lt;moduleSerial&gt;</t>
+  </si>
+  <si>
+    <t>&lt;consumableLot&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0%"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="167" formatCode="0"/>
-    <numFmt numFmtId="168" formatCode="dd\-mm\-yyyy;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd;@"/>
+    <numFmt numFmtId="165" formatCode="dd-mm-yyyy;@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="16"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <b/>
+      <charset val="204"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="16"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
+      <charset val="204"/>
       <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="16"/>
+      <charset val="1"/>
       <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <b/>
+      <charset val="1"/>
       <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -187,21 +173,21 @@
     </fill>
   </fills>
   <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="medium"/>
       <right style="medium"/>
       <top style="medium"/>
       <bottom style="medium"/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
@@ -209,217 +195,108 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="22">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="22">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="8">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Normal 2" xfId="20"/>
-    <cellStyle name="Normal 2 2" xfId="21"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K1009"/>
-  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="14.6" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.68359375" customHeight="1"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="12.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="15.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18.46"/>
+    <col min="1" max="1" width="20.31" customWidth="1"/>
+    <col min="2" max="2" width="37.46" customWidth="1"/>
+    <col min="3" max="3" width="16.15" customWidth="1"/>
+    <col min="4" max="4" width="36.69" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="7" width="12.84" customWidth="1"/>
+    <col min="8" max="8" width="12.84" style="1" customWidth="1"/>
+    <col min="9" max="10" width="15.84" style="2" customWidth="1"/>
+    <col min="11" max="11" width="18.46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="20.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="20.6" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -434,7 +311,7 @@
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" ht="15.9" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -449,7 +326,7 @@
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" ht="15.9" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -464,7 +341,7 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" ht="15.9" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
@@ -479,7 +356,7 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="15.9" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>4</v>
       </c>
@@ -494,7 +371,10 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="15.9" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
@@ -505,9 +385,9 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="16.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="16.3" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="7"/>
@@ -520,3077 +400,3072 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="31" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="16" t="s">
+    </row>
+    <row r="9" ht="15.9" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="B9" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="C9" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="D9" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="E9" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="F9" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="H9" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="20" t="s">
+      <c r="I9" s="20" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J9" s="20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H10" s="21"/>
     </row>
-    <row r="11" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H11" s="21"/>
     </row>
-    <row r="12" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H12" s="21"/>
     </row>
-    <row r="13" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H13" s="21"/>
     </row>
-    <row r="14" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H14" s="21"/>
     </row>
-    <row r="15" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H15" s="21"/>
     </row>
-    <row r="16" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H16" s="21"/>
     </row>
-    <row r="17" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H17" s="21"/>
     </row>
-    <row r="18" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H18" s="21"/>
     </row>
-    <row r="19" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H19" s="21"/>
     </row>
-    <row r="20" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H20" s="21"/>
     </row>
-    <row r="21" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H21" s="21"/>
     </row>
-    <row r="22" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H22" s="21"/>
     </row>
-    <row r="23" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H23" s="21"/>
     </row>
-    <row r="24" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H24" s="21"/>
     </row>
-    <row r="25" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H25" s="21"/>
     </row>
-    <row r="26" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H26" s="21"/>
     </row>
-    <row r="27" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H27" s="21"/>
     </row>
-    <row r="28" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H28" s="21"/>
     </row>
-    <row r="29" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H29" s="21"/>
     </row>
-    <row r="30" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H30" s="21"/>
     </row>
-    <row r="31" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H31" s="21"/>
     </row>
-    <row r="32" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H32" s="21"/>
     </row>
-    <row r="33" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H33" s="21"/>
     </row>
-    <row r="34" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H34" s="21"/>
     </row>
-    <row r="35" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H35" s="21"/>
     </row>
-    <row r="36" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H36" s="21"/>
     </row>
-    <row r="37" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H37" s="21"/>
     </row>
-    <row r="38" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H38" s="21"/>
     </row>
-    <row r="39" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H39" s="21"/>
     </row>
-    <row r="40" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H40" s="21"/>
     </row>
-    <row r="41" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H41" s="21"/>
     </row>
-    <row r="42" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H42" s="21"/>
     </row>
-    <row r="43" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H43" s="21"/>
     </row>
-    <row r="44" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H44" s="21"/>
     </row>
-    <row r="45" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H45" s="21"/>
     </row>
-    <row r="46" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H46" s="21"/>
     </row>
-    <row r="47" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H47" s="21"/>
     </row>
-    <row r="48" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H48" s="21"/>
     </row>
-    <row r="49" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H49" s="21"/>
     </row>
-    <row r="50" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H50" s="21"/>
     </row>
-    <row r="51" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H51" s="21"/>
     </row>
-    <row r="52" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H52" s="21"/>
     </row>
-    <row r="53" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H53" s="21"/>
     </row>
-    <row r="54" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H54" s="21"/>
     </row>
-    <row r="55" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H55" s="21"/>
     </row>
-    <row r="56" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H56" s="21"/>
     </row>
-    <row r="57" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H57" s="21"/>
     </row>
-    <row r="58" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H58" s="21"/>
     </row>
-    <row r="59" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H59" s="21"/>
     </row>
-    <row r="60" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H60" s="21"/>
     </row>
-    <row r="61" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H61" s="21"/>
     </row>
-    <row r="62" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H62" s="21"/>
     </row>
-    <row r="63" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H63" s="21"/>
     </row>
-    <row r="64" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H64" s="21"/>
     </row>
-    <row r="65" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H65" s="21"/>
     </row>
-    <row r="66" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H66" s="21"/>
     </row>
-    <row r="67" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H67" s="21"/>
     </row>
-    <row r="68" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H68" s="21"/>
     </row>
-    <row r="69" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H69" s="21"/>
     </row>
-    <row r="70" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H70" s="21"/>
     </row>
-    <row r="71" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H71" s="21"/>
     </row>
-    <row r="72" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H72" s="21"/>
     </row>
-    <row r="73" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H73" s="21"/>
     </row>
-    <row r="74" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H74" s="21"/>
     </row>
-    <row r="75" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H75" s="21"/>
     </row>
-    <row r="76" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H76" s="21"/>
     </row>
-    <row r="77" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H77" s="21"/>
     </row>
-    <row r="78" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H78" s="21"/>
     </row>
-    <row r="79" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H79" s="21"/>
     </row>
-    <row r="80" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H80" s="21"/>
     </row>
-    <row r="81" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H81" s="21"/>
     </row>
-    <row r="82" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H82" s="21"/>
     </row>
-    <row r="83" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H83" s="21"/>
     </row>
-    <row r="84" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H84" s="21"/>
     </row>
-    <row r="85" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H85" s="21"/>
     </row>
-    <row r="86" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H86" s="21"/>
     </row>
-    <row r="87" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H87" s="21"/>
     </row>
-    <row r="88" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H88" s="21"/>
     </row>
-    <row r="89" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H89" s="21"/>
     </row>
-    <row r="90" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H90" s="21"/>
     </row>
-    <row r="91" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H91" s="21"/>
     </row>
-    <row r="92" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H92" s="21"/>
     </row>
-    <row r="93" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H93" s="21"/>
     </row>
-    <row r="94" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H94" s="21"/>
     </row>
-    <row r="95" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H95" s="21"/>
     </row>
-    <row r="96" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H96" s="21"/>
     </row>
-    <row r="97" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H97" s="21"/>
     </row>
-    <row r="98" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H98" s="21"/>
     </row>
-    <row r="99" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H99" s="21"/>
     </row>
-    <row r="100" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H100" s="21"/>
     </row>
-    <row r="101" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H101" s="21"/>
     </row>
-    <row r="102" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H102" s="21"/>
     </row>
-    <row r="103" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H103" s="21"/>
     </row>
-    <row r="104" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H104" s="21"/>
     </row>
-    <row r="105" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H105" s="21"/>
     </row>
-    <row r="106" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H106" s="21"/>
     </row>
-    <row r="107" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H107" s="21"/>
     </row>
-    <row r="108" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H108" s="21"/>
     </row>
-    <row r="109" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H109" s="21"/>
     </row>
-    <row r="110" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H110" s="21"/>
     </row>
-    <row r="111" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H111" s="21"/>
     </row>
-    <row r="112" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H112" s="21"/>
     </row>
-    <row r="113" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H113" s="21"/>
     </row>
-    <row r="114" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H114" s="21"/>
     </row>
-    <row r="115" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H115" s="21"/>
     </row>
-    <row r="116" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H116" s="21"/>
     </row>
-    <row r="117" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H117" s="21"/>
     </row>
-    <row r="118" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H118" s="21"/>
     </row>
-    <row r="119" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H119" s="21"/>
     </row>
-    <row r="120" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H120" s="21"/>
     </row>
-    <row r="121" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H121" s="21"/>
     </row>
-    <row r="122" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H122" s="21"/>
     </row>
-    <row r="123" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H123" s="21"/>
     </row>
-    <row r="124" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H124" s="21"/>
     </row>
-    <row r="125" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H125" s="21"/>
     </row>
-    <row r="126" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H126" s="21"/>
     </row>
-    <row r="127" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H127" s="21"/>
     </row>
-    <row r="128" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H128" s="21"/>
     </row>
-    <row r="129" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H129" s="21"/>
     </row>
-    <row r="130" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H130" s="21"/>
     </row>
-    <row r="131" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H131" s="21"/>
     </row>
-    <row r="132" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H132" s="21"/>
     </row>
-    <row r="133" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H133" s="21"/>
     </row>
-    <row r="134" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H134" s="21"/>
     </row>
-    <row r="135" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H135" s="21"/>
     </row>
-    <row r="136" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H136" s="21"/>
     </row>
-    <row r="137" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H137" s="21"/>
     </row>
-    <row r="138" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H138" s="21"/>
     </row>
-    <row r="139" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H139" s="21"/>
     </row>
-    <row r="140" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H140" s="21"/>
     </row>
-    <row r="141" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H141" s="21"/>
     </row>
-    <row r="142" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H142" s="21"/>
     </row>
-    <row r="143" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H143" s="21"/>
     </row>
-    <row r="144" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H144" s="21"/>
     </row>
-    <row r="145" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H145" s="21"/>
     </row>
-    <row r="146" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H146" s="21"/>
     </row>
-    <row r="147" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H147" s="21"/>
     </row>
-    <row r="148" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H148" s="21"/>
     </row>
-    <row r="149" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H149" s="21"/>
     </row>
-    <row r="150" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H150" s="21"/>
     </row>
-    <row r="151" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H151" s="21"/>
     </row>
-    <row r="152" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H152" s="21"/>
     </row>
-    <row r="153" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H153" s="21"/>
     </row>
-    <row r="154" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H154" s="21"/>
     </row>
-    <row r="155" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H155" s="21"/>
     </row>
-    <row r="156" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H156" s="21"/>
     </row>
-    <row r="157" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H157" s="21"/>
     </row>
-    <row r="158" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H158" s="21"/>
     </row>
-    <row r="159" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H159" s="21"/>
     </row>
-    <row r="160" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H160" s="21"/>
     </row>
-    <row r="161" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H161" s="21"/>
     </row>
-    <row r="162" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H162" s="21"/>
     </row>
-    <row r="163" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H163" s="21"/>
     </row>
-    <row r="164" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H164" s="21"/>
     </row>
-    <row r="165" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H165" s="21"/>
     </row>
-    <row r="166" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H166" s="21"/>
     </row>
-    <row r="167" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H167" s="21"/>
     </row>
-    <row r="168" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H168" s="21"/>
     </row>
-    <row r="169" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H169" s="21"/>
     </row>
-    <row r="170" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H170" s="21"/>
     </row>
-    <row r="171" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H171" s="21"/>
     </row>
-    <row r="172" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H172" s="21"/>
     </row>
-    <row r="173" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H173" s="21"/>
     </row>
-    <row r="174" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H174" s="21"/>
     </row>
-    <row r="175" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H175" s="21"/>
     </row>
-    <row r="176" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H176" s="21"/>
     </row>
-    <row r="177" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H177" s="21"/>
     </row>
-    <row r="178" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H178" s="21"/>
     </row>
-    <row r="179" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H179" s="21"/>
     </row>
-    <row r="180" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H180" s="21"/>
     </row>
-    <row r="181" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H181" s="21"/>
     </row>
-    <row r="182" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H182" s="21"/>
     </row>
-    <row r="183" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H183" s="21"/>
     </row>
-    <row r="184" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H184" s="21"/>
     </row>
-    <row r="185" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H185" s="21"/>
     </row>
-    <row r="186" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H186" s="21"/>
     </row>
-    <row r="187" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H187" s="21"/>
     </row>
-    <row r="188" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H188" s="21"/>
     </row>
-    <row r="189" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H189" s="21"/>
     </row>
-    <row r="190" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H190" s="21"/>
     </row>
-    <row r="191" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H191" s="21"/>
     </row>
-    <row r="192" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H192" s="21"/>
     </row>
-    <row r="193" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H193" s="21"/>
     </row>
-    <row r="194" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H194" s="21"/>
     </row>
-    <row r="195" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H195" s="21"/>
     </row>
-    <row r="196" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H196" s="21"/>
     </row>
-    <row r="197" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H197" s="21"/>
     </row>
-    <row r="198" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H198" s="21"/>
     </row>
-    <row r="199" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H199" s="21"/>
     </row>
-    <row r="200" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H200" s="21"/>
     </row>
-    <row r="201" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H201" s="21"/>
     </row>
-    <row r="202" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H202" s="21"/>
     </row>
-    <row r="203" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H203" s="21"/>
     </row>
-    <row r="204" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H204" s="21"/>
     </row>
-    <row r="205" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H205" s="21"/>
     </row>
-    <row r="206" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H206" s="21"/>
     </row>
-    <row r="207" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H207" s="21"/>
     </row>
-    <row r="208" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H208" s="21"/>
     </row>
-    <row r="209" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H209" s="21"/>
     </row>
-    <row r="210" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H210" s="21"/>
     </row>
-    <row r="211" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H211" s="21"/>
     </row>
-    <row r="212" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H212" s="21"/>
     </row>
-    <row r="213" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H213" s="21"/>
     </row>
-    <row r="214" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H214" s="21"/>
     </row>
-    <row r="215" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H215" s="21"/>
     </row>
-    <row r="216" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H216" s="21"/>
     </row>
-    <row r="217" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H217" s="21"/>
     </row>
-    <row r="218" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H218" s="21"/>
     </row>
-    <row r="219" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H219" s="21"/>
     </row>
-    <row r="220" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H220" s="21"/>
     </row>
-    <row r="221" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H221" s="21"/>
     </row>
-    <row r="222" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H222" s="21"/>
     </row>
-    <row r="223" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H223" s="21"/>
     </row>
-    <row r="224" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H224" s="21"/>
     </row>
-    <row r="225" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H225" s="21"/>
     </row>
-    <row r="226" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H226" s="21"/>
     </row>
-    <row r="227" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H227" s="21"/>
     </row>
-    <row r="228" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H228" s="21"/>
     </row>
-    <row r="229" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H229" s="21"/>
     </row>
-    <row r="230" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H230" s="21"/>
     </row>
-    <row r="231" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H231" s="21"/>
     </row>
-    <row r="232" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H232" s="21"/>
     </row>
-    <row r="233" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H233" s="21"/>
     </row>
-    <row r="234" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H234" s="21"/>
     </row>
-    <row r="235" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H235" s="21"/>
     </row>
-    <row r="236" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H236" s="21"/>
     </row>
-    <row r="237" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H237" s="21"/>
     </row>
-    <row r="238" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H238" s="21"/>
     </row>
-    <row r="239" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H239" s="21"/>
     </row>
-    <row r="240" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H240" s="21"/>
     </row>
-    <row r="241" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H241" s="21"/>
     </row>
-    <row r="242" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H242" s="21"/>
     </row>
-    <row r="243" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H243" s="21"/>
     </row>
-    <row r="244" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H244" s="21"/>
     </row>
-    <row r="245" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H245" s="21"/>
     </row>
-    <row r="246" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H246" s="21"/>
     </row>
-    <row r="247" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H247" s="21"/>
     </row>
-    <row r="248" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H248" s="21"/>
     </row>
-    <row r="249" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H249" s="21"/>
     </row>
-    <row r="250" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H250" s="21"/>
     </row>
-    <row r="251" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H251" s="21"/>
     </row>
-    <row r="252" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H252" s="21"/>
     </row>
-    <row r="253" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H253" s="21"/>
     </row>
-    <row r="254" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H254" s="21"/>
     </row>
-    <row r="255" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H255" s="21"/>
     </row>
-    <row r="256" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H256" s="21"/>
     </row>
-    <row r="257" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H257" s="21"/>
     </row>
-    <row r="258" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H258" s="21"/>
     </row>
-    <row r="259" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H259" s="21"/>
     </row>
-    <row r="260" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H260" s="21"/>
     </row>
-    <row r="261" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H261" s="21"/>
     </row>
-    <row r="262" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H262" s="21"/>
     </row>
-    <row r="263" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H263" s="21"/>
     </row>
-    <row r="264" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H264" s="21"/>
     </row>
-    <row r="265" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H265" s="21"/>
     </row>
-    <row r="266" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H266" s="21"/>
     </row>
-    <row r="267" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H267" s="21"/>
     </row>
-    <row r="268" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H268" s="21"/>
     </row>
-    <row r="269" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H269" s="21"/>
     </row>
-    <row r="270" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H270" s="21"/>
     </row>
-    <row r="271" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H271" s="21"/>
     </row>
-    <row r="272" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H272" s="21"/>
     </row>
-    <row r="273" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H273" s="21"/>
     </row>
-    <row r="274" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H274" s="21"/>
     </row>
-    <row r="275" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H275" s="21"/>
     </row>
-    <row r="276" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H276" s="21"/>
     </row>
-    <row r="277" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H277" s="21"/>
     </row>
-    <row r="278" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H278" s="21"/>
     </row>
-    <row r="279" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H279" s="21"/>
     </row>
-    <row r="280" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H280" s="21"/>
     </row>
-    <row r="281" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H281" s="21"/>
     </row>
-    <row r="282" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H282" s="21"/>
     </row>
-    <row r="283" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H283" s="21"/>
     </row>
-    <row r="284" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H284" s="21"/>
     </row>
-    <row r="285" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H285" s="21"/>
     </row>
-    <row r="286" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H286" s="21"/>
     </row>
-    <row r="287" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H287" s="21"/>
     </row>
-    <row r="288" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H288" s="21"/>
     </row>
-    <row r="289" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H289" s="21"/>
     </row>
-    <row r="290" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H290" s="21"/>
     </row>
-    <row r="291" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H291" s="21"/>
     </row>
-    <row r="292" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H292" s="21"/>
     </row>
-    <row r="293" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H293" s="21"/>
     </row>
-    <row r="294" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H294" s="21"/>
     </row>
-    <row r="295" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H295" s="21"/>
     </row>
-    <row r="296" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H296" s="21"/>
     </row>
-    <row r="297" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H297" s="21"/>
     </row>
-    <row r="298" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H298" s="21"/>
     </row>
-    <row r="299" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H299" s="21"/>
     </row>
-    <row r="300" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H300" s="21"/>
     </row>
-    <row r="301" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H301" s="21"/>
     </row>
-    <row r="302" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H302" s="21"/>
     </row>
-    <row r="303" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H303" s="21"/>
     </row>
-    <row r="304" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H304" s="21"/>
     </row>
-    <row r="305" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H305" s="21"/>
     </row>
-    <row r="306" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H306" s="21"/>
     </row>
-    <row r="307" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="307" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H307" s="21"/>
     </row>
-    <row r="308" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H308" s="21"/>
     </row>
-    <row r="309" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H309" s="21"/>
     </row>
-    <row r="310" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H310" s="21"/>
     </row>
-    <row r="311" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H311" s="21"/>
     </row>
-    <row r="312" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H312" s="21"/>
     </row>
-    <row r="313" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H313" s="21"/>
     </row>
-    <row r="314" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H314" s="21"/>
     </row>
-    <row r="315" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H315" s="21"/>
     </row>
-    <row r="316" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H316" s="21"/>
     </row>
-    <row r="317" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H317" s="21"/>
     </row>
-    <row r="318" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H318" s="21"/>
     </row>
-    <row r="319" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="319" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H319" s="21"/>
     </row>
-    <row r="320" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H320" s="21"/>
     </row>
-    <row r="321" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H321" s="21"/>
     </row>
-    <row r="322" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="322" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H322" s="21"/>
     </row>
-    <row r="323" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H323" s="21"/>
     </row>
-    <row r="324" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H324" s="21"/>
     </row>
-    <row r="325" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="325" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H325" s="21"/>
     </row>
-    <row r="326" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="326" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H326" s="21"/>
     </row>
-    <row r="327" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="327" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H327" s="21"/>
     </row>
-    <row r="328" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="328" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H328" s="21"/>
     </row>
-    <row r="329" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="329" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H329" s="21"/>
     </row>
-    <row r="330" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="330" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H330" s="21"/>
     </row>
-    <row r="331" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="331" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H331" s="21"/>
     </row>
-    <row r="332" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="332" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H332" s="21"/>
     </row>
-    <row r="333" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="333" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H333" s="21"/>
     </row>
-    <row r="334" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H334" s="21"/>
     </row>
-    <row r="335" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H335" s="21"/>
     </row>
-    <row r="336" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H336" s="21"/>
     </row>
-    <row r="337" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H337" s="21"/>
     </row>
-    <row r="338" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H338" s="21"/>
     </row>
-    <row r="339" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="339" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H339" s="21"/>
     </row>
-    <row r="340" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H340" s="21"/>
     </row>
-    <row r="341" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="341" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H341" s="21"/>
     </row>
-    <row r="342" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="342" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H342" s="21"/>
     </row>
-    <row r="343" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="343" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H343" s="21"/>
     </row>
-    <row r="344" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H344" s="21"/>
     </row>
-    <row r="345" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="345" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H345" s="21"/>
     </row>
-    <row r="346" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="346" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H346" s="21"/>
     </row>
-    <row r="347" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H347" s="21"/>
     </row>
-    <row r="348" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H348" s="21"/>
     </row>
-    <row r="349" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="349" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H349" s="21"/>
     </row>
-    <row r="350" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H350" s="21"/>
     </row>
-    <row r="351" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H351" s="21"/>
     </row>
-    <row r="352" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="352" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H352" s="21"/>
     </row>
-    <row r="353" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H353" s="21"/>
     </row>
-    <row r="354" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H354" s="21"/>
     </row>
-    <row r="355" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H355" s="21"/>
     </row>
-    <row r="356" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="356" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H356" s="21"/>
     </row>
-    <row r="357" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H357" s="21"/>
     </row>
-    <row r="358" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H358" s="21"/>
     </row>
-    <row r="359" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="359" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H359" s="21"/>
     </row>
-    <row r="360" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H360" s="21"/>
     </row>
-    <row r="361" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="361" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H361" s="21"/>
     </row>
-    <row r="362" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="362" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H362" s="21"/>
     </row>
-    <row r="363" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="363" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H363" s="21"/>
     </row>
-    <row r="364" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H364" s="21"/>
     </row>
-    <row r="365" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="365" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H365" s="21"/>
     </row>
-    <row r="366" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H366" s="21"/>
     </row>
-    <row r="367" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="367" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H367" s="21"/>
     </row>
-    <row r="368" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="368" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H368" s="21"/>
     </row>
-    <row r="369" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H369" s="21"/>
     </row>
-    <row r="370" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H370" s="21"/>
     </row>
-    <row r="371" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="371" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H371" s="21"/>
     </row>
-    <row r="372" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="372" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H372" s="21"/>
     </row>
-    <row r="373" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H373" s="21"/>
     </row>
-    <row r="374" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="374" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H374" s="21"/>
     </row>
-    <row r="375" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="375" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H375" s="21"/>
     </row>
-    <row r="376" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H376" s="21"/>
     </row>
-    <row r="377" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="377" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H377" s="21"/>
     </row>
-    <row r="378" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="378" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H378" s="21"/>
     </row>
-    <row r="379" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="379" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H379" s="21"/>
     </row>
-    <row r="380" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="380" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H380" s="21"/>
     </row>
-    <row r="381" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H381" s="21"/>
     </row>
-    <row r="382" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="382" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H382" s="21"/>
     </row>
-    <row r="383" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="383" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H383" s="21"/>
     </row>
-    <row r="384" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="384" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H384" s="21"/>
     </row>
-    <row r="385" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H385" s="21"/>
     </row>
-    <row r="386" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="386" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H386" s="21"/>
     </row>
-    <row r="387" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="387" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H387" s="21"/>
     </row>
-    <row r="388" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H388" s="21"/>
     </row>
-    <row r="389" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H389" s="21"/>
     </row>
-    <row r="390" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H390" s="21"/>
     </row>
-    <row r="391" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H391" s="21"/>
     </row>
-    <row r="392" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H392" s="21"/>
     </row>
-    <row r="393" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="393" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H393" s="21"/>
     </row>
-    <row r="394" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="394" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H394" s="21"/>
     </row>
-    <row r="395" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="395" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H395" s="21"/>
     </row>
-    <row r="396" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="396" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H396" s="21"/>
     </row>
-    <row r="397" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="397" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H397" s="21"/>
     </row>
-    <row r="398" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="398" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H398" s="21"/>
     </row>
-    <row r="399" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="399" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H399" s="21"/>
     </row>
-    <row r="400" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="400" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H400" s="21"/>
     </row>
-    <row r="401" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H401" s="21"/>
     </row>
-    <row r="402" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="402" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H402" s="21"/>
     </row>
-    <row r="403" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="403" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H403" s="21"/>
     </row>
-    <row r="404" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="404" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H404" s="21"/>
     </row>
-    <row r="405" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="405" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H405" s="21"/>
     </row>
-    <row r="406" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="406" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H406" s="21"/>
     </row>
-    <row r="407" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H407" s="21"/>
     </row>
-    <row r="408" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="408" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H408" s="21"/>
     </row>
-    <row r="409" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="409" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H409" s="21"/>
     </row>
-    <row r="410" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="410" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H410" s="21"/>
     </row>
-    <row r="411" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H411" s="21"/>
     </row>
-    <row r="412" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="412" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H412" s="21"/>
     </row>
-    <row r="413" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="413" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H413" s="21"/>
     </row>
-    <row r="414" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="414" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H414" s="21"/>
     </row>
-    <row r="415" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H415" s="21"/>
     </row>
-    <row r="416" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H416" s="21"/>
     </row>
-    <row r="417" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="417" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H417" s="21"/>
     </row>
-    <row r="418" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="418" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H418" s="21"/>
     </row>
-    <row r="419" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="419" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H419" s="21"/>
     </row>
-    <row r="420" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="420" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H420" s="21"/>
     </row>
-    <row r="421" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="421" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H421" s="21"/>
     </row>
-    <row r="422" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="422" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H422" s="21"/>
     </row>
-    <row r="423" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="423" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H423" s="21"/>
     </row>
-    <row r="424" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="424" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H424" s="21"/>
     </row>
-    <row r="425" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="425" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H425" s="21"/>
     </row>
-    <row r="426" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="426" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H426" s="21"/>
     </row>
-    <row r="427" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H427" s="21"/>
     </row>
-    <row r="428" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="428" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H428" s="21"/>
     </row>
-    <row r="429" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H429" s="21"/>
     </row>
-    <row r="430" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H430" s="21"/>
     </row>
-    <row r="431" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="431" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H431" s="21"/>
     </row>
-    <row r="432" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="432" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H432" s="21"/>
     </row>
-    <row r="433" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H433" s="21"/>
     </row>
-    <row r="434" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="434" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H434" s="21"/>
     </row>
-    <row r="435" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="435" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H435" s="21"/>
     </row>
-    <row r="436" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="436" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H436" s="21"/>
     </row>
-    <row r="437" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H437" s="21"/>
     </row>
-    <row r="438" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="438" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H438" s="21"/>
     </row>
-    <row r="439" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H439" s="21"/>
     </row>
-    <row r="440" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="440" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H440" s="21"/>
     </row>
-    <row r="441" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="441" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H441" s="21"/>
     </row>
-    <row r="442" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H442" s="21"/>
     </row>
-    <row r="443" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="443" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H443" s="21"/>
     </row>
-    <row r="444" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="444" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H444" s="21"/>
     </row>
-    <row r="445" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="445" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H445" s="21"/>
     </row>
-    <row r="446" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="446" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H446" s="21"/>
     </row>
-    <row r="447" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="447" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H447" s="21"/>
     </row>
-    <row r="448" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="448" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H448" s="21"/>
     </row>
-    <row r="449" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="449" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H449" s="21"/>
     </row>
-    <row r="450" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="450" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H450" s="21"/>
     </row>
-    <row r="451" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="451" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H451" s="21"/>
     </row>
-    <row r="452" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="452" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H452" s="21"/>
     </row>
-    <row r="453" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="453" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H453" s="21"/>
     </row>
-    <row r="454" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="454" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H454" s="21"/>
     </row>
-    <row r="455" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="455" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H455" s="21"/>
     </row>
-    <row r="456" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="456" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H456" s="21"/>
     </row>
-    <row r="457" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H457" s="21"/>
     </row>
-    <row r="458" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="458" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H458" s="21"/>
     </row>
-    <row r="459" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="459" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H459" s="21"/>
     </row>
-    <row r="460" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="460" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H460" s="21"/>
     </row>
-    <row r="461" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="461" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H461" s="21"/>
     </row>
-    <row r="462" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="462" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H462" s="21"/>
     </row>
-    <row r="463" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="463" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H463" s="21"/>
     </row>
-    <row r="464" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="464" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H464" s="21"/>
     </row>
-    <row r="465" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="465" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H465" s="21"/>
     </row>
-    <row r="466" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="466" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H466" s="21"/>
     </row>
-    <row r="467" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="467" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H467" s="21"/>
     </row>
-    <row r="468" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="468" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H468" s="21"/>
     </row>
-    <row r="469" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="469" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H469" s="21"/>
     </row>
-    <row r="470" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H470" s="21"/>
     </row>
-    <row r="471" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="471" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H471" s="21"/>
     </row>
-    <row r="472" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="472" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H472" s="21"/>
     </row>
-    <row r="473" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="473" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H473" s="21"/>
     </row>
-    <row r="474" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="474" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H474" s="21"/>
     </row>
-    <row r="475" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="475" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H475" s="21"/>
     </row>
-    <row r="476" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="476" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H476" s="21"/>
     </row>
-    <row r="477" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="477" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H477" s="21"/>
     </row>
-    <row r="478" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="478" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H478" s="21"/>
     </row>
-    <row r="479" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="479" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H479" s="21"/>
     </row>
-    <row r="480" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H480" s="21"/>
     </row>
-    <row r="481" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="481" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H481" s="21"/>
     </row>
-    <row r="482" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="482" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H482" s="21"/>
     </row>
-    <row r="483" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="483" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H483" s="21"/>
     </row>
-    <row r="484" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H484" s="21"/>
     </row>
-    <row r="485" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="485" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H485" s="21"/>
     </row>
-    <row r="486" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="486" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H486" s="21"/>
     </row>
-    <row r="487" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="487" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H487" s="21"/>
     </row>
-    <row r="488" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="488" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H488" s="21"/>
     </row>
-    <row r="489" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="489" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H489" s="21"/>
     </row>
-    <row r="490" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="490" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H490" s="21"/>
     </row>
-    <row r="491" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="491" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H491" s="21"/>
     </row>
-    <row r="492" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="492" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H492" s="21"/>
     </row>
-    <row r="493" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="493" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H493" s="21"/>
     </row>
-    <row r="494" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="494" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H494" s="21"/>
     </row>
-    <row r="495" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="495" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H495" s="21"/>
     </row>
-    <row r="496" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="496" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H496" s="21"/>
     </row>
-    <row r="497" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="497" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H497" s="21"/>
     </row>
-    <row r="498" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="498" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H498" s="21"/>
     </row>
-    <row r="499" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="499" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H499" s="21"/>
     </row>
-    <row r="500" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="500" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H500" s="21"/>
     </row>
-    <row r="501" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="501" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H501" s="21"/>
     </row>
-    <row r="502" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="502" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H502" s="21"/>
     </row>
-    <row r="503" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="503" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H503" s="21"/>
     </row>
-    <row r="504" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="504" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H504" s="21"/>
     </row>
-    <row r="505" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="505" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H505" s="21"/>
     </row>
-    <row r="506" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="506" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H506" s="21"/>
     </row>
-    <row r="507" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="507" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H507" s="21"/>
     </row>
-    <row r="508" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="508" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H508" s="21"/>
     </row>
-    <row r="509" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="509" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H509" s="21"/>
     </row>
-    <row r="510" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="510" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H510" s="21"/>
     </row>
-    <row r="511" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="511" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H511" s="21"/>
     </row>
-    <row r="512" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="512" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H512" s="21"/>
     </row>
-    <row r="513" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="513" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H513" s="21"/>
     </row>
-    <row r="514" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="514" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H514" s="21"/>
     </row>
-    <row r="515" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="515" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H515" s="21"/>
     </row>
-    <row r="516" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="516" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H516" s="21"/>
     </row>
-    <row r="517" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="517" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H517" s="21"/>
     </row>
-    <row r="518" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="518" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H518" s="21"/>
     </row>
-    <row r="519" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="519" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H519" s="21"/>
     </row>
-    <row r="520" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="520" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H520" s="21"/>
     </row>
-    <row r="521" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="521" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H521" s="21"/>
     </row>
-    <row r="522" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="522" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H522" s="21"/>
     </row>
-    <row r="523" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="523" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H523" s="21"/>
     </row>
-    <row r="524" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="524" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H524" s="21"/>
     </row>
-    <row r="525" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="525" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H525" s="21"/>
     </row>
-    <row r="526" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="526" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H526" s="21"/>
     </row>
-    <row r="527" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="527" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H527" s="21"/>
     </row>
-    <row r="528" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="528" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H528" s="21"/>
     </row>
-    <row r="529" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="529" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H529" s="21"/>
     </row>
-    <row r="530" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="530" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H530" s="21"/>
     </row>
-    <row r="531" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="531" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H531" s="21"/>
     </row>
-    <row r="532" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="532" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H532" s="21"/>
     </row>
-    <row r="533" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="533" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H533" s="21"/>
     </row>
-    <row r="534" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="534" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H534" s="21"/>
     </row>
-    <row r="535" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="535" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H535" s="21"/>
     </row>
-    <row r="536" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="536" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H536" s="21"/>
     </row>
-    <row r="537" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="537" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H537" s="21"/>
     </row>
-    <row r="538" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="538" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H538" s="21"/>
     </row>
-    <row r="539" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="539" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H539" s="21"/>
     </row>
-    <row r="540" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="540" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H540" s="21"/>
     </row>
-    <row r="541" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="541" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H541" s="21"/>
     </row>
-    <row r="542" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="542" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H542" s="21"/>
     </row>
-    <row r="543" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="543" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H543" s="21"/>
     </row>
-    <row r="544" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="544" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H544" s="21"/>
     </row>
-    <row r="545" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="545" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H545" s="21"/>
     </row>
-    <row r="546" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="546" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H546" s="21"/>
     </row>
-    <row r="547" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="547" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H547" s="21"/>
     </row>
-    <row r="548" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="548" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H548" s="21"/>
     </row>
-    <row r="549" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="549" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H549" s="21"/>
     </row>
-    <row r="550" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="550" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H550" s="21"/>
     </row>
-    <row r="551" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="551" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H551" s="21"/>
     </row>
-    <row r="552" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="552" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H552" s="21"/>
     </row>
-    <row r="553" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="553" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H553" s="21"/>
     </row>
-    <row r="554" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="554" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H554" s="21"/>
     </row>
-    <row r="555" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="555" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H555" s="21"/>
     </row>
-    <row r="556" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="556" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H556" s="21"/>
     </row>
-    <row r="557" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="557" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H557" s="21"/>
     </row>
-    <row r="558" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="558" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H558" s="21"/>
     </row>
-    <row r="559" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="559" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H559" s="21"/>
     </row>
-    <row r="560" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="560" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H560" s="21"/>
     </row>
-    <row r="561" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="561" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H561" s="21"/>
     </row>
-    <row r="562" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="562" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H562" s="21"/>
     </row>
-    <row r="563" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="563" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H563" s="21"/>
     </row>
-    <row r="564" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="564" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H564" s="21"/>
     </row>
-    <row r="565" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="565" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H565" s="21"/>
     </row>
-    <row r="566" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="566" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H566" s="21"/>
     </row>
-    <row r="567" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="567" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H567" s="21"/>
     </row>
-    <row r="568" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="568" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H568" s="21"/>
     </row>
-    <row r="569" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="569" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H569" s="21"/>
     </row>
-    <row r="570" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="570" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H570" s="21"/>
     </row>
-    <row r="571" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="571" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H571" s="21"/>
     </row>
-    <row r="572" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="572" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H572" s="21"/>
     </row>
-    <row r="573" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="573" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H573" s="21"/>
     </row>
-    <row r="574" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="574" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H574" s="21"/>
     </row>
-    <row r="575" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="575" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H575" s="21"/>
     </row>
-    <row r="576" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="576" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H576" s="21"/>
     </row>
-    <row r="577" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="577" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H577" s="21"/>
     </row>
-    <row r="578" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="578" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H578" s="21"/>
     </row>
-    <row r="579" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="579" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H579" s="21"/>
     </row>
-    <row r="580" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="580" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H580" s="21"/>
     </row>
-    <row r="581" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="581" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H581" s="21"/>
     </row>
-    <row r="582" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="582" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H582" s="21"/>
     </row>
-    <row r="583" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="583" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H583" s="21"/>
     </row>
-    <row r="584" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="584" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H584" s="21"/>
     </row>
-    <row r="585" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="585" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H585" s="21"/>
     </row>
-    <row r="586" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="586" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H586" s="21"/>
     </row>
-    <row r="587" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="587" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H587" s="21"/>
     </row>
-    <row r="588" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="588" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H588" s="21"/>
     </row>
-    <row r="589" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="589" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H589" s="21"/>
     </row>
-    <row r="590" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="590" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H590" s="21"/>
     </row>
-    <row r="591" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="591" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H591" s="21"/>
     </row>
-    <row r="592" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="592" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H592" s="21"/>
     </row>
-    <row r="593" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="593" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H593" s="21"/>
     </row>
-    <row r="594" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="594" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H594" s="21"/>
     </row>
-    <row r="595" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="595" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H595" s="21"/>
     </row>
-    <row r="596" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="596" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H596" s="21"/>
     </row>
-    <row r="597" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="597" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H597" s="21"/>
     </row>
-    <row r="598" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="598" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H598" s="21"/>
     </row>
-    <row r="599" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="599" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H599" s="21"/>
     </row>
-    <row r="600" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="600" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H600" s="21"/>
     </row>
-    <row r="601" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="601" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H601" s="21"/>
     </row>
-    <row r="602" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="602" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H602" s="21"/>
     </row>
-    <row r="603" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="603" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H603" s="21"/>
     </row>
-    <row r="604" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="604" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H604" s="21"/>
     </row>
-    <row r="605" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="605" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H605" s="21"/>
     </row>
-    <row r="606" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="606" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H606" s="21"/>
     </row>
-    <row r="607" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="607" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H607" s="21"/>
     </row>
-    <row r="608" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="608" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H608" s="21"/>
     </row>
-    <row r="609" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="609" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H609" s="21"/>
     </row>
-    <row r="610" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="610" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H610" s="21"/>
     </row>
-    <row r="611" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="611" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H611" s="21"/>
     </row>
-    <row r="612" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="612" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H612" s="21"/>
     </row>
-    <row r="613" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="613" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H613" s="21"/>
     </row>
-    <row r="614" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="614" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H614" s="21"/>
     </row>
-    <row r="615" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="615" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H615" s="21"/>
     </row>
-    <row r="616" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="616" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H616" s="21"/>
     </row>
-    <row r="617" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="617" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H617" s="21"/>
     </row>
-    <row r="618" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="618" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H618" s="21"/>
     </row>
-    <row r="619" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="619" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H619" s="21"/>
     </row>
-    <row r="620" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="620" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H620" s="21"/>
     </row>
-    <row r="621" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="621" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H621" s="21"/>
     </row>
-    <row r="622" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="622" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H622" s="21"/>
     </row>
-    <row r="623" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="623" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H623" s="21"/>
     </row>
-    <row r="624" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="624" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H624" s="21"/>
     </row>
-    <row r="625" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="625" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H625" s="21"/>
     </row>
-    <row r="626" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="626" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H626" s="21"/>
     </row>
-    <row r="627" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="627" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H627" s="21"/>
     </row>
-    <row r="628" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="628" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H628" s="21"/>
     </row>
-    <row r="629" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="629" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H629" s="21"/>
     </row>
-    <row r="630" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="630" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H630" s="21"/>
     </row>
-    <row r="631" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="631" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H631" s="21"/>
     </row>
-    <row r="632" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="632" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H632" s="21"/>
     </row>
-    <row r="633" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="633" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H633" s="21"/>
     </row>
-    <row r="634" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="634" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H634" s="21"/>
     </row>
-    <row r="635" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="635" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H635" s="21"/>
     </row>
-    <row r="636" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="636" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H636" s="21"/>
     </row>
-    <row r="637" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="637" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H637" s="21"/>
     </row>
-    <row r="638" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="638" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H638" s="21"/>
     </row>
-    <row r="639" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="639" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H639" s="21"/>
     </row>
-    <row r="640" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="640" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H640" s="21"/>
     </row>
-    <row r="641" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="641" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H641" s="21"/>
     </row>
-    <row r="642" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="642" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H642" s="21"/>
     </row>
-    <row r="643" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="643" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H643" s="21"/>
     </row>
-    <row r="644" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="644" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H644" s="21"/>
     </row>
-    <row r="645" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="645" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H645" s="21"/>
     </row>
-    <row r="646" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="646" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H646" s="21"/>
     </row>
-    <row r="647" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="647" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H647" s="21"/>
     </row>
-    <row r="648" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="648" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H648" s="21"/>
     </row>
-    <row r="649" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="649" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H649" s="21"/>
     </row>
-    <row r="650" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="650" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H650" s="21"/>
     </row>
-    <row r="651" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="651" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H651" s="21"/>
     </row>
-    <row r="652" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="652" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H652" s="21"/>
     </row>
-    <row r="653" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="653" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H653" s="21"/>
     </row>
-    <row r="654" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="654" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H654" s="21"/>
     </row>
-    <row r="655" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="655" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H655" s="21"/>
     </row>
-    <row r="656" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="656" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H656" s="21"/>
     </row>
-    <row r="657" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="657" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H657" s="21"/>
     </row>
-    <row r="658" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="658" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H658" s="21"/>
     </row>
-    <row r="659" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="659" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H659" s="21"/>
     </row>
-    <row r="660" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="660" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H660" s="21"/>
     </row>
-    <row r="661" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="661" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H661" s="21"/>
     </row>
-    <row r="662" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="662" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H662" s="21"/>
     </row>
-    <row r="663" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="663" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H663" s="21"/>
     </row>
-    <row r="664" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="664" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H664" s="21"/>
     </row>
-    <row r="665" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="665" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H665" s="21"/>
     </row>
-    <row r="666" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="666" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H666" s="21"/>
     </row>
-    <row r="667" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="667" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H667" s="21"/>
     </row>
-    <row r="668" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="668" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H668" s="21"/>
     </row>
-    <row r="669" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="669" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H669" s="21"/>
     </row>
-    <row r="670" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="670" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H670" s="21"/>
     </row>
-    <row r="671" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="671" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H671" s="21"/>
     </row>
-    <row r="672" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="672" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H672" s="21"/>
     </row>
-    <row r="673" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="673" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H673" s="21"/>
     </row>
-    <row r="674" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="674" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H674" s="21"/>
     </row>
-    <row r="675" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="675" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H675" s="21"/>
     </row>
-    <row r="676" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="676" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H676" s="21"/>
     </row>
-    <row r="677" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="677" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H677" s="21"/>
     </row>
-    <row r="678" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="678" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H678" s="21"/>
     </row>
-    <row r="679" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="679" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H679" s="21"/>
     </row>
-    <row r="680" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="680" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H680" s="21"/>
     </row>
-    <row r="681" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="681" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H681" s="21"/>
     </row>
-    <row r="682" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="682" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H682" s="21"/>
     </row>
-    <row r="683" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="683" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H683" s="21"/>
     </row>
-    <row r="684" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="684" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H684" s="21"/>
     </row>
-    <row r="685" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="685" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H685" s="21"/>
     </row>
-    <row r="686" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="686" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H686" s="21"/>
     </row>
-    <row r="687" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="687" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H687" s="21"/>
     </row>
-    <row r="688" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="688" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H688" s="21"/>
     </row>
-    <row r="689" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="689" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H689" s="21"/>
     </row>
-    <row r="690" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="690" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H690" s="21"/>
     </row>
-    <row r="691" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="691" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H691" s="21"/>
     </row>
-    <row r="692" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="692" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H692" s="21"/>
     </row>
-    <row r="693" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="693" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H693" s="21"/>
     </row>
-    <row r="694" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="694" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H694" s="21"/>
     </row>
-    <row r="695" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="695" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H695" s="21"/>
     </row>
-    <row r="696" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="696" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H696" s="21"/>
     </row>
-    <row r="697" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="697" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H697" s="21"/>
     </row>
-    <row r="698" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="698" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H698" s="21"/>
     </row>
-    <row r="699" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="699" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H699" s="21"/>
     </row>
-    <row r="700" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="700" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H700" s="21"/>
     </row>
-    <row r="701" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="701" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H701" s="21"/>
     </row>
-    <row r="702" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="702" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H702" s="21"/>
     </row>
-    <row r="703" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="703" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H703" s="21"/>
     </row>
-    <row r="704" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="704" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H704" s="21"/>
     </row>
-    <row r="705" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="705" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H705" s="21"/>
     </row>
-    <row r="706" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="706" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H706" s="21"/>
     </row>
-    <row r="707" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="707" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H707" s="21"/>
     </row>
-    <row r="708" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="708" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H708" s="21"/>
     </row>
-    <row r="709" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="709" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H709" s="21"/>
     </row>
-    <row r="710" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="710" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H710" s="21"/>
     </row>
-    <row r="711" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="711" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H711" s="21"/>
     </row>
-    <row r="712" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="712" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H712" s="21"/>
     </row>
-    <row r="713" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="713" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H713" s="21"/>
     </row>
-    <row r="714" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="714" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H714" s="21"/>
     </row>
-    <row r="715" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="715" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H715" s="21"/>
     </row>
-    <row r="716" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="716" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H716" s="21"/>
     </row>
-    <row r="717" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="717" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H717" s="21"/>
     </row>
-    <row r="718" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="718" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H718" s="21"/>
     </row>
-    <row r="719" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="719" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H719" s="21"/>
     </row>
-    <row r="720" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="720" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H720" s="21"/>
     </row>
-    <row r="721" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="721" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H721" s="21"/>
     </row>
-    <row r="722" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="722" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H722" s="21"/>
     </row>
-    <row r="723" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="723" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H723" s="21"/>
     </row>
-    <row r="724" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="724" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H724" s="21"/>
     </row>
-    <row r="725" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="725" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H725" s="21"/>
     </row>
-    <row r="726" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="726" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H726" s="21"/>
     </row>
-    <row r="727" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="727" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H727" s="21"/>
     </row>
-    <row r="728" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="728" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H728" s="21"/>
     </row>
-    <row r="729" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="729" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H729" s="21"/>
     </row>
-    <row r="730" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="730" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H730" s="21"/>
     </row>
-    <row r="731" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="731" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H731" s="21"/>
     </row>
-    <row r="732" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="732" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H732" s="21"/>
     </row>
-    <row r="733" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="733" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H733" s="21"/>
     </row>
-    <row r="734" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="734" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H734" s="21"/>
     </row>
-    <row r="735" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="735" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H735" s="21"/>
     </row>
-    <row r="736" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="736" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H736" s="21"/>
     </row>
-    <row r="737" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="737" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H737" s="21"/>
     </row>
-    <row r="738" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="738" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H738" s="21"/>
     </row>
-    <row r="739" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="739" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H739" s="21"/>
     </row>
-    <row r="740" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="740" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H740" s="21"/>
     </row>
-    <row r="741" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="741" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H741" s="21"/>
     </row>
-    <row r="742" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="742" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H742" s="21"/>
     </row>
-    <row r="743" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="743" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H743" s="21"/>
     </row>
-    <row r="744" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="744" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H744" s="21"/>
     </row>
-    <row r="745" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="745" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H745" s="21"/>
     </row>
-    <row r="746" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="746" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H746" s="21"/>
     </row>
-    <row r="747" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="747" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H747" s="21"/>
     </row>
-    <row r="748" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="748" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H748" s="21"/>
     </row>
-    <row r="749" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="749" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H749" s="21"/>
     </row>
-    <row r="750" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="750" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H750" s="21"/>
     </row>
-    <row r="751" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="751" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H751" s="21"/>
     </row>
-    <row r="752" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="752" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H752" s="21"/>
     </row>
-    <row r="753" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="753" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H753" s="21"/>
     </row>
-    <row r="754" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="754" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H754" s="21"/>
     </row>
-    <row r="755" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="755" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H755" s="21"/>
     </row>
-    <row r="756" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="756" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H756" s="21"/>
     </row>
-    <row r="757" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="757" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H757" s="21"/>
     </row>
-    <row r="758" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="758" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H758" s="21"/>
     </row>
-    <row r="759" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="759" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H759" s="21"/>
     </row>
-    <row r="760" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="760" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H760" s="21"/>
     </row>
-    <row r="761" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="761" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H761" s="21"/>
     </row>
-    <row r="762" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="762" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H762" s="21"/>
     </row>
-    <row r="763" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="763" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H763" s="21"/>
     </row>
-    <row r="764" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="764" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H764" s="21"/>
     </row>
-    <row r="765" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="765" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H765" s="21"/>
     </row>
-    <row r="766" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="766" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H766" s="21"/>
     </row>
-    <row r="767" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="767" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H767" s="21"/>
     </row>
-    <row r="768" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="768" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H768" s="21"/>
     </row>
-    <row r="769" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="769" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H769" s="21"/>
     </row>
-    <row r="770" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="770" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H770" s="21"/>
     </row>
-    <row r="771" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="771" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H771" s="21"/>
     </row>
-    <row r="772" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="772" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H772" s="21"/>
     </row>
-    <row r="773" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="773" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H773" s="21"/>
     </row>
-    <row r="774" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="774" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H774" s="21"/>
     </row>
-    <row r="775" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="775" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H775" s="21"/>
     </row>
-    <row r="776" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="776" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H776" s="21"/>
     </row>
-    <row r="777" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="777" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H777" s="21"/>
     </row>
-    <row r="778" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="778" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H778" s="21"/>
     </row>
-    <row r="779" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="779" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H779" s="21"/>
     </row>
-    <row r="780" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="780" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H780" s="21"/>
     </row>
-    <row r="781" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="781" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H781" s="21"/>
     </row>
-    <row r="782" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="782" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H782" s="21"/>
     </row>
-    <row r="783" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="783" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H783" s="21"/>
     </row>
-    <row r="784" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="784" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H784" s="21"/>
     </row>
-    <row r="785" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="785" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H785" s="21"/>
     </row>
-    <row r="786" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="786" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H786" s="21"/>
     </row>
-    <row r="787" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="787" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H787" s="21"/>
     </row>
-    <row r="788" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="788" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H788" s="21"/>
     </row>
-    <row r="789" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="789" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H789" s="21"/>
     </row>
-    <row r="790" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="790" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H790" s="21"/>
     </row>
-    <row r="791" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="791" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H791" s="21"/>
     </row>
-    <row r="792" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="792" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H792" s="21"/>
     </row>
-    <row r="793" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="793" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H793" s="21"/>
     </row>
-    <row r="794" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="794" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H794" s="21"/>
     </row>
-    <row r="795" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="795" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H795" s="21"/>
     </row>
-    <row r="796" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="796" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H796" s="21"/>
     </row>
-    <row r="797" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="797" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H797" s="21"/>
     </row>
-    <row r="798" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="798" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H798" s="21"/>
     </row>
-    <row r="799" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="799" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H799" s="21"/>
     </row>
-    <row r="800" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="800" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H800" s="21"/>
     </row>
-    <row r="801" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="801" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H801" s="21"/>
     </row>
-    <row r="802" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="802" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H802" s="21"/>
     </row>
-    <row r="803" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="803" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H803" s="21"/>
     </row>
-    <row r="804" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="804" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H804" s="21"/>
     </row>
-    <row r="805" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="805" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H805" s="21"/>
     </row>
-    <row r="806" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="806" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H806" s="21"/>
     </row>
-    <row r="807" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="807" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H807" s="21"/>
     </row>
-    <row r="808" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="808" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H808" s="21"/>
     </row>
-    <row r="809" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="809" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H809" s="21"/>
     </row>
-    <row r="810" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="810" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H810" s="21"/>
     </row>
-    <row r="811" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="811" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H811" s="21"/>
     </row>
-    <row r="812" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="812" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H812" s="21"/>
     </row>
-    <row r="813" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="813" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H813" s="21"/>
     </row>
-    <row r="814" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="814" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H814" s="21"/>
     </row>
-    <row r="815" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="815" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H815" s="21"/>
     </row>
-    <row r="816" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="816" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H816" s="21"/>
     </row>
-    <row r="817" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="817" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H817" s="21"/>
     </row>
-    <row r="818" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="818" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H818" s="21"/>
     </row>
-    <row r="819" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="819" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H819" s="21"/>
     </row>
-    <row r="820" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="820" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H820" s="21"/>
     </row>
-    <row r="821" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="821" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H821" s="21"/>
     </row>
-    <row r="822" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="822" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H822" s="21"/>
     </row>
-    <row r="823" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="823" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H823" s="21"/>
     </row>
-    <row r="824" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="824" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H824" s="21"/>
     </row>
-    <row r="825" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="825" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H825" s="21"/>
     </row>
-    <row r="826" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="826" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H826" s="21"/>
     </row>
-    <row r="827" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="827" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H827" s="21"/>
     </row>
-    <row r="828" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="828" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H828" s="21"/>
     </row>
-    <row r="829" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="829" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H829" s="21"/>
     </row>
-    <row r="830" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="830" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H830" s="21"/>
     </row>
-    <row r="831" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="831" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H831" s="21"/>
     </row>
-    <row r="832" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="832" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H832" s="21"/>
     </row>
-    <row r="833" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="833" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H833" s="21"/>
     </row>
-    <row r="834" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="834" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H834" s="21"/>
     </row>
-    <row r="835" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="835" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H835" s="21"/>
     </row>
-    <row r="836" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="836" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H836" s="21"/>
     </row>
-    <row r="837" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="837" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H837" s="21"/>
     </row>
-    <row r="838" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="838" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H838" s="21"/>
     </row>
-    <row r="839" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="839" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H839" s="21"/>
     </row>
-    <row r="840" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="840" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H840" s="21"/>
     </row>
-    <row r="841" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="841" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H841" s="21"/>
     </row>
-    <row r="842" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="842" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H842" s="21"/>
     </row>
-    <row r="843" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="843" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H843" s="21"/>
     </row>
-    <row r="844" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="844" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H844" s="21"/>
     </row>
-    <row r="845" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="845" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H845" s="21"/>
     </row>
-    <row r="846" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="846" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H846" s="21"/>
     </row>
-    <row r="847" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="847" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H847" s="21"/>
     </row>
-    <row r="848" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="848" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H848" s="21"/>
     </row>
-    <row r="849" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="849" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H849" s="21"/>
     </row>
-    <row r="850" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="850" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H850" s="21"/>
     </row>
-    <row r="851" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="851" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H851" s="21"/>
     </row>
-    <row r="852" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="852" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H852" s="21"/>
     </row>
-    <row r="853" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="853" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H853" s="21"/>
     </row>
-    <row r="854" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="854" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H854" s="21"/>
     </row>
-    <row r="855" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="855" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H855" s="21"/>
     </row>
-    <row r="856" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="856" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H856" s="21"/>
     </row>
-    <row r="857" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="857" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H857" s="21"/>
     </row>
-    <row r="858" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="858" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H858" s="21"/>
     </row>
-    <row r="859" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="859" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H859" s="21"/>
     </row>
-    <row r="860" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="860" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H860" s="21"/>
     </row>
-    <row r="861" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="861" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H861" s="21"/>
     </row>
-    <row r="862" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="862" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H862" s="21"/>
     </row>
-    <row r="863" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="863" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H863" s="21"/>
     </row>
-    <row r="864" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="864" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H864" s="21"/>
     </row>
-    <row r="865" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="865" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H865" s="21"/>
     </row>
-    <row r="866" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="866" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H866" s="21"/>
     </row>
-    <row r="867" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="867" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H867" s="21"/>
     </row>
-    <row r="868" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="868" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H868" s="21"/>
     </row>
-    <row r="869" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="869" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H869" s="21"/>
     </row>
-    <row r="870" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="870" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H870" s="21"/>
     </row>
-    <row r="871" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="871" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H871" s="21"/>
     </row>
-    <row r="872" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="872" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H872" s="21"/>
     </row>
-    <row r="873" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="873" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H873" s="21"/>
     </row>
-    <row r="874" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="874" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H874" s="21"/>
     </row>
-    <row r="875" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="875" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H875" s="21"/>
     </row>
-    <row r="876" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="876" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H876" s="21"/>
     </row>
-    <row r="877" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="877" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H877" s="21"/>
     </row>
-    <row r="878" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="878" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H878" s="21"/>
     </row>
-    <row r="879" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="879" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H879" s="21"/>
     </row>
-    <row r="880" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="880" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H880" s="21"/>
     </row>
-    <row r="881" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="881" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H881" s="21"/>
     </row>
-    <row r="882" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="882" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H882" s="21"/>
     </row>
-    <row r="883" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="883" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H883" s="21"/>
     </row>
-    <row r="884" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="884" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H884" s="21"/>
     </row>
-    <row r="885" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="885" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H885" s="21"/>
     </row>
-    <row r="886" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="886" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H886" s="21"/>
     </row>
-    <row r="887" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="887" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H887" s="21"/>
     </row>
-    <row r="888" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="888" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H888" s="21"/>
     </row>
-    <row r="889" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="889" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H889" s="21"/>
     </row>
-    <row r="890" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="890" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H890" s="21"/>
     </row>
-    <row r="891" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="891" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H891" s="21"/>
     </row>
-    <row r="892" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="892" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H892" s="21"/>
     </row>
-    <row r="893" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="893" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H893" s="21"/>
     </row>
-    <row r="894" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="894" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H894" s="21"/>
     </row>
-    <row r="895" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="895" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H895" s="21"/>
     </row>
-    <row r="896" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="896" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H896" s="21"/>
     </row>
-    <row r="897" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="897" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H897" s="21"/>
     </row>
-    <row r="898" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="898" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H898" s="21"/>
     </row>
-    <row r="899" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="899" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H899" s="21"/>
     </row>
-    <row r="900" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="900" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H900" s="21"/>
     </row>
-    <row r="901" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="901" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H901" s="21"/>
     </row>
-    <row r="902" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="902" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H902" s="21"/>
     </row>
-    <row r="903" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="903" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H903" s="21"/>
     </row>
-    <row r="904" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="904" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H904" s="21"/>
     </row>
-    <row r="905" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="905" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H905" s="21"/>
     </row>
-    <row r="906" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="906" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H906" s="21"/>
     </row>
-    <row r="907" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="907" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H907" s="21"/>
     </row>
-    <row r="908" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="908" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H908" s="21"/>
     </row>
-    <row r="909" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="909" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H909" s="21"/>
     </row>
-    <row r="910" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="910" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H910" s="21"/>
     </row>
-    <row r="911" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="911" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H911" s="21"/>
     </row>
-    <row r="912" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="912" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H912" s="21"/>
     </row>
-    <row r="913" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="913" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H913" s="21"/>
     </row>
-    <row r="914" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="914" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H914" s="21"/>
     </row>
-    <row r="915" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="915" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H915" s="21"/>
     </row>
-    <row r="916" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="916" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H916" s="21"/>
     </row>
-    <row r="917" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="917" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H917" s="21"/>
     </row>
-    <row r="918" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="918" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H918" s="21"/>
     </row>
-    <row r="919" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="919" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H919" s="21"/>
     </row>
-    <row r="920" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="920" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H920" s="21"/>
     </row>
-    <row r="921" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="921" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H921" s="21"/>
     </row>
-    <row r="922" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="922" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H922" s="21"/>
     </row>
-    <row r="923" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="923" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H923" s="21"/>
     </row>
-    <row r="924" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="924" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H924" s="21"/>
     </row>
-    <row r="925" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="925" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H925" s="21"/>
     </row>
-    <row r="926" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="926" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H926" s="21"/>
     </row>
-    <row r="927" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="927" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H927" s="21"/>
     </row>
-    <row r="928" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="928" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H928" s="21"/>
     </row>
-    <row r="929" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="929" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H929" s="21"/>
     </row>
-    <row r="930" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="930" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H930" s="21"/>
     </row>
-    <row r="931" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="931" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H931" s="21"/>
     </row>
-    <row r="932" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="932" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H932" s="21"/>
     </row>
-    <row r="933" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="933" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H933" s="21"/>
     </row>
-    <row r="934" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="934" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H934" s="21"/>
     </row>
-    <row r="935" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="935" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H935" s="21"/>
     </row>
-    <row r="936" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="936" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H936" s="21"/>
     </row>
-    <row r="937" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="937" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H937" s="21"/>
     </row>
-    <row r="938" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="938" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H938" s="21"/>
     </row>
-    <row r="939" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="939" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H939" s="21"/>
     </row>
-    <row r="940" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="940" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H940" s="21"/>
     </row>
-    <row r="941" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="941" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H941" s="21"/>
     </row>
-    <row r="942" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="942" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H942" s="21"/>
     </row>
-    <row r="943" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="943" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H943" s="21"/>
     </row>
-    <row r="944" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="944" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H944" s="21"/>
     </row>
-    <row r="945" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="945" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H945" s="21"/>
     </row>
-    <row r="946" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="946" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H946" s="21"/>
     </row>
-    <row r="947" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="947" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H947" s="21"/>
     </row>
-    <row r="948" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="948" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H948" s="21"/>
     </row>
-    <row r="949" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="949" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H949" s="21"/>
     </row>
-    <row r="950" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="950" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H950" s="21"/>
     </row>
-    <row r="951" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="951" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H951" s="21"/>
     </row>
-    <row r="952" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="952" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H952" s="21"/>
     </row>
-    <row r="953" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="953" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H953" s="21"/>
     </row>
-    <row r="954" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="954" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H954" s="21"/>
     </row>
-    <row r="955" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="955" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H955" s="21"/>
     </row>
-    <row r="956" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="956" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H956" s="21"/>
     </row>
-    <row r="957" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="957" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H957" s="21"/>
     </row>
-    <row r="958" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="958" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H958" s="21"/>
     </row>
-    <row r="959" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="959" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H959" s="21"/>
     </row>
-    <row r="960" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="960" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H960" s="21"/>
     </row>
-    <row r="961" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="961" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H961" s="21"/>
     </row>
-    <row r="962" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="962" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H962" s="21"/>
     </row>
-    <row r="963" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="963" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H963" s="21"/>
     </row>
-    <row r="964" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="964" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H964" s="21"/>
     </row>
-    <row r="965" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="965" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H965" s="21"/>
     </row>
-    <row r="966" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="966" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H966" s="21"/>
     </row>
-    <row r="967" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="967" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H967" s="21"/>
     </row>
-    <row r="968" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="968" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H968" s="21"/>
     </row>
-    <row r="969" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="969" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H969" s="21"/>
     </row>
-    <row r="970" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="970" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H970" s="21"/>
     </row>
-    <row r="971" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="971" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H971" s="21"/>
     </row>
-    <row r="972" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="972" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H972" s="21"/>
     </row>
-    <row r="973" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="973" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H973" s="21"/>
     </row>
-    <row r="974" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="974" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H974" s="21"/>
     </row>
-    <row r="975" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="975" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H975" s="21"/>
     </row>
-    <row r="976" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="976" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H976" s="21"/>
     </row>
-    <row r="977" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="977" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H977" s="21"/>
     </row>
-    <row r="978" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="978" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H978" s="21"/>
     </row>
-    <row r="979" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="979" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H979" s="21"/>
     </row>
-    <row r="980" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="980" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H980" s="21"/>
     </row>
-    <row r="981" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="981" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H981" s="21"/>
     </row>
-    <row r="982" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="982" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H982" s="21"/>
     </row>
-    <row r="983" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="983" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H983" s="21"/>
     </row>
-    <row r="984" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="984" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H984" s="21"/>
     </row>
-    <row r="985" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="985" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H985" s="21"/>
     </row>
-    <row r="986" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="986" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H986" s="21"/>
     </row>
-    <row r="987" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="987" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H987" s="21"/>
     </row>
-    <row r="988" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="988" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H988" s="21"/>
     </row>
-    <row r="989" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="989" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H989" s="21"/>
     </row>
-    <row r="990" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="990" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H990" s="21"/>
     </row>
-    <row r="991" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="991" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H991" s="21"/>
     </row>
-    <row r="992" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="992" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H992" s="21"/>
     </row>
-    <row r="993" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="993" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H993" s="21"/>
     </row>
-    <row r="994" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="994" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H994" s="21"/>
     </row>
-    <row r="995" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="995" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H995" s="21"/>
     </row>
-    <row r="996" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="996" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H996" s="21"/>
     </row>
-    <row r="997" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="997" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H997" s="21"/>
     </row>
-    <row r="998" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="998" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H998" s="21"/>
     </row>
-    <row r="999" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="999" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H999" s="21"/>
     </row>
-    <row r="1000" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1000" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H1000" s="21"/>
     </row>
-    <row r="1001" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1001" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H1001" s="21"/>
     </row>
-    <row r="1002" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1002" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H1002" s="21"/>
     </row>
-    <row r="1003" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1003" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H1003" s="21"/>
     </row>
-    <row r="1004" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1004" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H1004" s="21"/>
     </row>
-    <row r="1005" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1005" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H1005" s="21"/>
     </row>
-    <row r="1006" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1006" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H1006" s="21"/>
     </row>
-    <row r="1007" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1007" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H1007" s="21"/>
     </row>
-    <row r="1008" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1008" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H1008" s="21"/>
     </row>
-    <row r="1009" customFormat="false" ht="14.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1009" ht="14.6" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H1009" s="21"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/genexpert_issues/es.xlsx
+++ b/api/templates/genexpert_issues/es.xlsx
@@ -228,7 +228,7 @@
       <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" wrapText="1" shrinkToFit="1"/>

--- a/api/templates/genexpert_issues/es.xlsx
+++ b/api/templates/genexpert_issues/es.xlsx
@@ -31,7 +31,7 @@
     <t>Sitios: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Dispositivos dados de baja: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
